--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -8143,7 +8143,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8188,7 +8187,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/Steam桌面端产品定位与信息架构.md</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8196,7 +8195,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8249,7 +8247,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8302,7 +8299,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8355,7 +8351,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8408,7 +8403,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/Steam身份账号绑定与安全会话.md</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8338,17 +8338,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Unity 启动、窗口化、最小化/恢复、托盘、通知、低打扰后台挂机</t>
+          <t>窗口/托盘/主界面占位/通知接口；04A～04F Windows Development Build 与冒烟已完成</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -8401,6 +8406,348 @@
       <c r="J143" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04A</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Unity 工程基线与 Windows 构建</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>目录约定、DesktopMain、Player Settings、gitignore、构建菜单</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04B</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>应用生命周期与窗口模式</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>普通窗口/全屏/无边框、配置保存、关闭进托盘</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04C</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>托盘与后台挂机容器</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Win32 托盘菜单；隐藏后降帧；会话生命周期占位接口</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04D</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Unity 主界面与功能占位</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>运行时 UGUI：鱼塘/好友/鱼获/设置四入口可进出</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04E</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>桌面设置与通知接口</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>通知偏好持久化；鱼咬钩/好友邀请/连接错误模拟</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-04F</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Unity Windows 性能与发布验证</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Windows Development Build、窗口/托盘/设置/通知/后台降帧冒烟已完成</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/空鱼塘休眠与生态离线补算.md</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -8360,7 +8360,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8406,6 +8406,11 @@
       <c r="J143" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5899,7 +5899,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -5947,7 +5947,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6009,7 +6013,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -6024,7 +6028,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Unity移植P1·契约工程化</t>
+          <t>Unity 移植 P1·契约工程化</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6044,7 +6048,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI·Socket目录·C# DTO</t>
+          <t>Unity/Node/shared Socket 契约、C# DTO、服务端权威边界与兼容策略；Debug：补齐 phase/重连状态同步</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -6057,12 +6061,16 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -6077,7 +6085,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Unity移植P2·网络薄客户端</t>
+          <t>Unity 移植 P2·网络薄客户端</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6097,7 +6105,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Socket进塘闭环·钓一条入库</t>
+          <t>Steam JWT Socket 登录、进塘、钓鱼、咬钩、领取、背包更新与断线重连；Debug：修复 fish_bite 时序、重复收杆和空钓位 waiting</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -6110,12 +6118,16 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6163,12 +6175,16 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6216,12 +6232,16 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -6269,7 +6289,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -8199,7 +8223,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8245,6 +8269,11 @@
       <c r="J140" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -8751,6 +8780,63 @@
         </is>
       </c>
       <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BUG-21</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>桌面端关闭后进程残留</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>关闭按钮真正退出；托盘显式隐藏；单实例互斥；清理托盘线程</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-桌面端关闭后进程残留.md</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -14532,7 +14618,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -14550,7 +14636,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -14622,7 +14712,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -14640,7 +14730,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -14665,7 +14759,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -14683,7 +14777,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -14708,7 +14806,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -14726,7 +14824,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -14751,7 +14853,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -14769,7 +14871,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -14794,7 +14900,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -14812,7 +14918,11 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -8280,7 +8280,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8315,17 +8315,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>好友邀请进入 Lobby；Lobby 保存 pondId；Node 仍负责鱼塘权威</t>
+          <t>实现完成；Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；双 Steam 账号验收已跳过</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/Steam好友Lobby邀请与鱼塘映射.md</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8844,6 +8844,120 @@
       <c r="K150" t="inlineStr">
         <is>
           <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BUG-22</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Steam Lobby 创建权限拒绝与状态残留</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>细分 Lobby 权限错误；校验 Steam 绑定；创建失败回滚 CurrentLobbyId/pondId；不影响鱼塘生命周期</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-SteamLobby创建权限与状态残留.md</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-06</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>功能优化</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Steam Lobby 生命周期与邀请反馈优化</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>本版本跳过；不进入开发排期，后续如有正式 Lobby 产品方案再重新立项</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam Lobby生命周期与邀请反馈优化.md</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -8119,7 +8119,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已文档化</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Steam 独立游戏定位；Unity Windows 桌面助手；Steam 身份/Lobby；Node 权威服务；空鱼塘离线补算</t>
+          <t>规划已完成；实际 Unity 表现层拆分为 STEAM-DESKTOP-07，已完成子需求不重复开发</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8165,13 +8165,18 @@
       <c r="J138" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已文档化</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8186,7 +8191,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Steam 独立游戏定位与桌面助手信息架构</t>
+          <t>2D 多人社交桌面宠物定位、鱼塘场景与信息架构</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8206,7 +8211,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>上班族挂机、好友交流、低打扰通知；定义窗口/托盘/后台/主循环</t>
+          <t>规划已完成；桌面宠物、多人鱼塘、右键菜单与弹窗实现转入 STEAM-DESKTOP-07</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8217,6 +8222,11 @@
       <c r="J139" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8357,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8461,7 +8471,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8518,7 +8528,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8575,7 +8585,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8632,7 +8642,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8689,7 +8699,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8746,7 +8756,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>架构</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8960,6 +8970,376 @@
           <t>2026-08-13</t>
         </is>
       </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-ART-01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>美术</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>桌面宠物与鱼塘视觉资源替换</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>提供猫咪宠物、鱼塘环境和基础视觉资源；其他 UI 先由程序使用通用资源</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物UI需求拆分.md</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07A</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>桌面宠物主视图与鱼塘入口</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；复用已完成桌面壳</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07B</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2D 鱼塘环境与自己的猫咪</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07C</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>同塘玩家宠物与状态同步</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07D</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>桌面宠物右键菜单</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07E</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>桌面宠物功能弹窗层</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07F</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>桌面宠物主流程与恢复验收</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -6127,7 +6127,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Tile·相机·序列帧；承接REF-SCENE-1</t>
+          <t>架构出口由 STEAM-DESKTOP-07B/07C 承接；Tile、相机、序列帧、多人排序和真实网络状态表现尚未完成</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>地图·背包商店·社交·排行榜</t>
+          <t>架构出口由 STEAM-DESKTOP-07A/07D/07E/07F 承接；Unity 主循环尚未完成 Expo 脱离验收</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>商店构建·client-logs·退役RN</t>
+          <t>架构出口由 STEAM-DESKTOP-07F 及后续发布验收承接；Steam 可提交包、日志和回滚方案尚未完成</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -8290,7 +8290,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>验收中</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>实现完成；Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；双 Steam 账号验收已跳过</t>
+          <t>Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；实现已完成，双 Steam 账号验收待补</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -6127,7 +6127,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>架构出口由 STEAM-DESKTOP-07B/07C 承接；Tile、相机、序列帧、多人排序和真实网络状态表现尚未完成</t>
+          <t>Tile·相机·序列帧；承接REF-SCENE-1</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>架构出口由 STEAM-DESKTOP-07A/07D/07E/07F 承接；Unity 主循环尚未完成 Expo 脱离验收</t>
+          <t>地图·背包商店·社交·排行榜</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>架构出口由 STEAM-DESKTOP-07F 及后续发布验收承接；Steam 可提交包、日志和回滚方案尚未完成</t>
+          <t>商店构建·client-logs·退役RN</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -8290,7 +8290,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>验收中</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；实现已完成，双 Steam 账号验收待补</t>
+          <t>实现完成；Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；双 Steam 账号验收已跳过</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -5899,7 +5899,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>实现完成；Lobby 仅映射 pondId，房主/成员离开不关闭鱼塘；Node/DB 负责鱼塘权威、休眠与离线补算；双 Steam 账号验收已跳过</t>
+          <t>核心功能验收完成：Lobby 创建/加入、邀请与 pondId 映射、权限拒绝、Lobby 失效后重新进塘、房主离开不删除鱼塘；双 Steam 联调因缺少第二测试账号跳过</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；复用已完成桌面壳</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已定稿</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L159"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9340,6 +9340,59 @@
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07G</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>原生桌面宠物 Overlay</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9026,7 +9026,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>480×320 登录入口；登录后显示 1280×720 主窗口、小猫状态栏和底部横向按钮；进入鱼塘调用原生 Overlay 并隐藏主窗口；序列帧状态机与 Overlay 共用 petVisualState</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9074,12 +9074,16 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9114,7 +9118,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>在 960×480 Overlay 中显示池塘环境、钓位、自己的宠物和钓鱼表现；猫咪基准 128×128；pond_snapshot 驱动，快照更新不重建场景对象</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9127,7 +9131,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9167,7 +9175,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
+          <t>在 Overlay 中渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9220,7 +9228,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay/主窗口产品区域提供右键菜单；支持打开主窗口、鱼塘、好友、背包、图鉴、设置、托盘和退出</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9273,7 +9281,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
+          <t>主窗口底部按钮行进入好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9326,7 +9334,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>验收 480×320 登录、1280×720 主窗口、960×480 Overlay、窗口切换、挂机、通知和断线恢复</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9344,7 +9352,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9379,7 +9387,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>独立 WPF/Win32 Overlay；默认 960×480，承载鱼塘和猫咪表现；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令；已修复退出卡死与隐藏窗口 CMD</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9392,7 +9400,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9026,7 +9026,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>480×320 登录入口；登录后显示 1280×720 主窗口、小猫状态栏和底部横向按钮；进入鱼塘调用原生 Overlay 并隐藏主窗口；序列帧状态机与 Overlay 共用 petVisualState</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9074,16 +9074,12 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9118,7 +9114,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>在 960×480 Overlay 中显示池塘环境、钓位、自己的宠物和钓鱼表现；猫咪基准 128×128；pond_snapshot 驱动，快照更新不重建场景对象</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9131,11 +9127,7 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9175,7 +9167,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>在 Overlay 中渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
+          <t>渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9228,7 +9220,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>在 Overlay/主窗口产品区域提供右键菜单；支持打开主窗口、鱼塘、好友、背包、图鉴、设置、托盘和退出</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9281,7 +9273,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>主窗口底部按钮行进入好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
+          <t>好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9334,7 +9326,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>验收 480×320 登录、1280×720 主窗口、960×480 Overlay、窗口切换、挂机、通知和断线恢复</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9352,7 +9344,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9387,7 +9379,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；默认 960×480，承载鱼塘和猫咪表现；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令；已修复退出卡死与隐藏窗口 CMD</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9400,11 +9392,7 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
+      <c r="K160" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9167,7 +9167,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>渲染 pond_user_joined/left/updated；显示同塘玩家宠物、昵称和基础状态</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9132,7 +9132,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9180,7 +9180,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9189,7 +9189,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9237,7 +9237,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9031,17 +9031,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-ART-02</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>美术</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Overlay 场景布局管线</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9056,25 +9056,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>Unity 960×480 Canvas Prefab 导出布局 JSON；Overlay 按像素表摆图与钓位，有表则停用 MapToScene</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面Overlay场景布局管线.md</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9084,7 +9083,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9094,7 +9093,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9114,7 +9113,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9132,12 +9131,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9147,7 +9146,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9167,7 +9166,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9180,11 +9179,7 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9194,7 +9189,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9204,7 +9199,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9224,7 +9219,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9239,19 +9234,19 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9261,7 +9256,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>桌面宠物功能弹窗层</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9281,7 +9276,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置弹窗；打开关闭不得触发 leave_pond</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9294,17 +9289,21 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9314,7 +9313,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9334,12 +9333,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9347,7 +9346,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9357,50 +9360,103 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-07F</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>桌面宠物主流程与恢复验收</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J161" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9078,7 +9078,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9126,12 +9126,16 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9179,7 +9183,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9348,7 +9356,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9416,7 +9416,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9464,7 +9464,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9363,7 +9363,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9411,7 +9411,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9083,17 +9083,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9113,22 +9113,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9425,54 +9425,486 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-07F</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>桌面宠物主流程与恢复验收</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="K162" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08A</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>世界地图与鱼塘选择</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08B</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>商店与装备</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08C</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>动态墙与好友动态</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>PanelSocialFeed：公共/好友动态、点赞、评论、删除评论；不塞进 PanelSocial</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08D</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>排行榜</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>PanelLeaderboard：日榜/周榜/鱼塘榜/稀有鱼榜与我的排名；分数以服务端为准</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9856,7 +9856,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9904,7 +9904,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9534,7 +9534,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9582,7 +9582,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9591,7 +9591,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9639,7 +9639,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9913,6 +9917,59 @@
           <t>2026-08-17</t>
         </is>
       </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08I</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bug 修复 / 功能优化</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>鱼塘退出与跨塘切换优化</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；优化 Named Pipe 与 Socket 反馈延迟</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9083,17 +9083,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9113,22 +9113,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9450,22 +9450,22 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9507,22 +9507,22 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9584,19 +9584,19 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9621,17 +9621,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>PanelSocialFeed：公共/好友动态、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9639,11 +9639,7 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9653,7 +9649,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9663,7 +9659,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9683,12 +9679,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelLeaderboard：日榜/周榜/鱼塘榜/稀有鱼榜与我的排名；分数以服务端为准</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9706,7 +9702,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9716,7 +9712,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9736,12 +9732,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日榜/周榜/鱼塘榜/稀有鱼榜与我的排名；分数以服务端为准</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9754,12 +9750,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9769,7 +9765,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9784,17 +9780,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9802,7 +9798,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9869,17 +9869,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9921,7 +9921,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；优化 Named Pipe 与 Socket 反馈延迟</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9969,7 +9969,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9697,7 +9697,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9745,7 +9745,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9591,7 +9591,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9639,7 +9639,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9648,7 +9648,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日榜/周榜/鱼塘榜/稀有鱼榜与我的排名；分数以服务端为准</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9696,7 +9696,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5280,7 +5280,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>首页入口·独立页·领奖台·仅日/周·删稀有·周榜改最大鱼</t>
+          <t>首页入口、独立页、领奖台、仅日/周、删稀有 UI、周榜改最大鱼</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -9078,12 +9078,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-09A</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Overlay 玩家右键菜单</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9108,39 +9108,34 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>右键同塘玩家：资料、加好友、私聊、点赞；Overlay IPC → Unity 权威</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-09AOverlay玩家右键菜单.md</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-09B</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9150,7 +9145,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay 悬停状态与钓鱼时长</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9165,39 +9160,34 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>他人默认无状态；悬停 300ms Tooltip；IPC 扩展 sessionFishingMs/phase</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-09BOverlay悬停状态与钓鱼时长.md</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-09C</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9207,7 +9197,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>Overlay 鱼塘聊天气泡与输入</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9222,39 +9212,34 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>Overlay 公屏最近消息气泡 + 紧凑输入；完整聊天仍主窗口；修订 07E</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-09COverlay鱼塘聊天气泡与输入.md</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-09D</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9264,7 +9249,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>Overlay 布局与角色表现优化</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9284,22 +9269,17 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>960×560；宠物 64px；昵称在上；默认状态/上钩圆环；悬停仅时长；左上纵向收纳菜单；Bot 无「·机」</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-09DOverlay布局与角色表现优化.md</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9291,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9321,7 +9301,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9341,12 +9321,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9356,7 +9336,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9348,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9378,7 +9358,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9398,7 +9378,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9413,7 +9393,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9405,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9435,7 +9415,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9450,27 +9430,27 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9462,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9492,7 +9472,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9512,22 +9492,22 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9519,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9549,7 +9529,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9569,22 +9549,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9576,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9606,7 +9586,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9621,27 +9601,27 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9633,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9663,7 +9643,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9683,22 +9663,22 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9690,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9720,7 +9700,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9735,17 +9715,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9755,7 +9735,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9747,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9777,7 +9757,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9797,12 +9777,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9812,7 +9792,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9804,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9834,7 +9814,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9849,17 +9829,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9869,7 +9849,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -9881,17 +9861,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9906,17 +9886,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9926,7 +9906,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -9938,50 +9918,278 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="J174" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -15207,7 +15415,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9078,7 +9078,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9124,13 +9124,18 @@
       <c r="J155" t="inlineStr">
         <is>
           <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9165,7 +9170,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>他人默认无状态；悬停 300ms Tooltip；IPC 扩展 sessionFishingMs/phase</t>
+          <t>悬停 300ms 仅时长 Tooltip；IPC sessionFishingMs/phase/hookDeadlineMs</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9176,13 +9181,18 @@
       <c r="J156" t="inlineStr">
         <is>
           <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9217,7 +9227,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Overlay 公屏最近消息气泡 + 紧凑输入；完整聊天仍主窗口；修订 07E</t>
+          <t>Overlay 公屏最近 20 条气泡 + 紧凑输入；IPC recentChats/send_pond_chat；完整聊天仍主窗口</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9228,13 +9238,18 @@
       <c r="J157" t="inlineStr">
         <is>
           <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9278,6 +9293,11 @@
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>公网联调与服务器地址配置</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9336,39 +9336,39 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>可配置 serverBaseUrl（server.json/环境变量）；本机开发可迁云；联调手册</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端公网联调与服务器地址配置.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-10A</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>本机公网映射联调（方案 A）</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9393,49 +9393,49 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>CGNAT不可行已废弃；设置页/检查脚本保留给局域网；外网改10B</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端本机公网映射联调.md</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-10B</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>运维联调</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>云服务器联调与切换（保留项）</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9450,27 +9450,22 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>暂缓；当前本机/局域网联机；上云仅改server.json切换；实施时再部署</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端云服务器联调保留.md</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9477,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9492,7 +9487,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9512,7 +9507,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9527,7 +9522,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9534,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9549,7 +9544,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9569,12 +9564,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9584,7 +9579,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9591,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9606,7 +9601,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9626,7 +9621,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9641,7 +9636,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9648,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9663,7 +9658,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9678,27 +9673,27 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9705,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9720,7 +9715,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9740,17 +9735,17 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9767,7 +9762,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9777,7 +9772,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9797,22 +9792,22 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9819,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9834,7 +9829,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9854,22 +9849,22 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9876,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9891,7 +9886,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9906,17 +9901,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9926,7 +9921,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9933,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9948,7 +9943,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9963,17 +9958,17 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9995,7 +9990,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10005,7 +10000,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10020,17 +10015,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10040,7 +10035,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10047,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10062,7 +10057,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10077,17 +10072,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10097,7 +10092,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -10109,17 +10104,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10134,17 +10129,17 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10154,7 +10149,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10166,54 +10161,543 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J177" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EPIC-FISH-V07</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>钓鱼玩法扩展 v0.7 索引</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>15 条覆盖与 R1 拆票索引；Steam 优先</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/钓鱼玩法扩展-v0.7-Epic.md</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>FEAT-PROG-01</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>鱼塘分级与玩家成长</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>七类塘、双熟练度、每2h扣费、新手塘、卖价公式、固定数值表导出</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/鱼塘分级与玩家成长.md</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FEAT-GEAR-01</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>钓具与鱼饵配置</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>竿弱加成与断竿买新、饵等级解锁按次扣金、船仅商店不可用</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/钓具与鱼饵配置.md</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08A2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>世界地图分区与进塘扣费确认</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>六区展示锁态、巨物暂闭、进塘扣费确认；读 ponds.json</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>FEAT-RISK-01</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>禁止钓鱼塘巡警事件</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/禁止钓鱼塘巡警事件.md</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>FEAT-SPOT-01</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>钓位点位线索文字泡</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Overlay 点位环境线索泡；等级/塘熟练度解锁；薄实现</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/钓位点位线索文字泡.md</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L183"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2030,6 +2030,11 @@
           <t>2026-07-12</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -9472,22 +9477,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>EPIC-FISH-V07</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>钓鱼玩法扩展 v0.7 索引</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9497,7 +9502,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9507,22 +9512,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>15 条覆盖与 R1 拆票索引；Steam 优先</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/钓鱼玩法扩展-v0.7-Epic.md</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>FEAT-PROG-01</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>鱼塘分级与玩家成长</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9564,34 +9564,34 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>七类塘、双熟练度、每2h扣费、新手塘、卖价公式、固定数值表导出</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/鱼塘分级与玩家成长.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>FEAT-GEAR-01</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>钓具与鱼饵配置</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9621,34 +9621,29 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>竿弱加成与断竿买新、饵等级解锁按次扣金、船仅商店不可用</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/钓具与鱼饵配置.md</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-08A2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9658,7 +9653,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>世界地图分区与进塘扣费确认</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9668,7 +9663,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9678,34 +9673,29 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>六区展示锁态、巨物暂闭、进塘扣费确认；读 ponds.json</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>FEAT-RISK-01</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9715,7 +9705,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>禁止钓鱼塘巡警事件</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9725,44 +9715,39 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/禁止钓鱼塘巡警事件.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>FEAT-SPOT-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9772,7 +9757,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>钓位点位线索文字泡</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9782,32 +9767,27 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>Overlay 点位环境线索泡；等级/塘熟练度解锁；薄实现</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/钓位点位线索文字泡.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9799,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-11</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9829,7 +9809,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>新手引导本地教学关</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9839,32 +9819,32 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>Overlay 本地教学关；5秒必上钩/圆圈；自动入包弹窗</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端-新手引导本地教学关.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9856,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9886,7 +9866,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9906,22 +9886,22 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9913,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9943,7 +9923,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9963,22 +9943,22 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9970,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10000,7 +9980,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10015,27 +9995,27 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10027,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10057,7 +10037,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10072,27 +10052,27 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10084,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10114,7 +10094,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10129,27 +10109,27 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10141,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10171,7 +10151,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10191,17 +10171,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10218,7 +10198,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10228,7 +10208,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10243,22 +10223,22 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10275,17 +10255,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10305,12 +10285,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10332,17 +10312,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10362,17 +10342,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10384,22 +10364,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EPIC-FISH-V07</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>钓鱼玩法扩展 v0.7 索引</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10409,40 +10389,44 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>15 条覆盖与 R1 拆票索引；Steam 优先</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓鱼玩法扩展-v0.7-Epic.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FEAT-PROG-01</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10452,7 +10436,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>鱼塘分级与玩家成长</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10462,40 +10446,44 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>七类塘、双熟练度、每2h扣费、新手塘、卖价公式、固定数值表导出</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘分级与玩家成长.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FEAT-GEAR-01</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10505,7 +10493,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>钓具与鱼饵配置</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10515,40 +10503,44 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>竿弱加成与断竿买新、饵等级解锁按次扣金、船仅商店不可用</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓具与鱼饵配置.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A2</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10558,7 +10550,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>世界地图分区与进塘扣费确认</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10568,7 +10560,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10578,30 +10570,34 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>六区展示锁态、巨物暂闭、进塘扣费确认；读 ponds.json</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FEAT-RISK-01</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10611,7 +10607,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>禁止钓鱼塘巡警事件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10621,50 +10617,54 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/禁止钓鱼塘巡警事件.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FEAT-SPOT-01</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>钓位点位线索文字泡</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10674,30 +10674,91 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Overlay 点位环境线索泡；等级/塘熟练度解锁；薄实现</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓位点位线索文字泡.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08I</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Bug 修复 / 功能优化</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>鱼塘退出与跨塘切换优化</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9586,7 +9586,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9632,13 +9632,18 @@
       <c r="J164" t="inlineStr">
         <is>
           <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9684,6 +9689,11 @@
       <c r="J165" t="inlineStr">
         <is>
           <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9735,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘</t>
+          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘；开发版设置一键出警</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9700,7 +9700,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘；开发版设置一键出警</t>
+          <t>巡警气泡10秒离塘免罚；超时罚款归零+当日禁塘；开发版禁止塘Overlay一键出警</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9746,6 +9746,11 @@
       <c r="J166" t="inlineStr">
         <is>
           <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L184"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9757,7 +9757,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Overlay 点位环境线索泡；等级/塘熟练度解锁；薄实现</t>
+          <t>坐席后聊天泡；文案表随机；habitat/activity两类经验</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9803,6 +9803,11 @@
       <c r="J167" t="inlineStr">
         <is>
           <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9876,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-12</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9881,7 +9886,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>玩法 Debug 菜单</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9891,32 +9896,32 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>开发版呼出菜单：升级/满级/塘熟练度/加钱/出警/鱼获/+2h扣费测</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-玩法Debug菜单.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9933,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9938,7 +9943,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9958,7 +9963,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9985,7 +9990,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9995,7 +10000,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10015,7 +10020,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10030,7 +10035,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10047,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10052,7 +10057,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10072,7 +10077,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10087,7 +10092,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10104,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10109,7 +10114,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10129,12 +10134,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10144,7 +10149,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10166,7 +10171,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10186,12 +10191,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10213,7 +10218,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10223,7 +10228,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10238,22 +10243,22 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10270,7 +10275,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10280,7 +10285,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10295,22 +10300,22 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10327,7 +10332,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10337,7 +10342,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10357,12 +10362,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10372,7 +10377,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10389,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10394,7 +10399,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10409,17 +10414,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10429,7 +10434,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10446,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10451,7 +10456,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10471,12 +10476,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10486,7 +10491,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10503,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10508,7 +10513,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10528,12 +10533,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10543,7 +10548,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10560,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10565,7 +10570,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10580,17 +10585,17 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10600,7 +10605,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10617,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10622,7 +10627,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10642,12 +10647,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10669,17 +10674,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10699,12 +10704,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10726,50 +10731,107 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I185" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="J185" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10836,6 +10836,165 @@
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FEAT-RETURN-01</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>回鱼机制</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>回塘增重、品质/尺寸准入、金≈卖价×0.7+熟练度；收杆+背包入口</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/回鱼机制.md</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>FEAT-GROUND-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>打窝机制</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Overlay并列循环打窝；50层非线性；0.5~1.5%/层曲线；附近鱼小幅尺寸</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/打窝机制.md</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>FEAT-ALBUM-01</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>钓鱼相册与成就</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>个人中心大改：资料+展示柜+图鉴+相册墙+成就；他人可见精选</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/钓鱼相册与成就.md</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L188"/>
+  <dimension ref="A1:L190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>FEAT-RETURN-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>回鱼机制</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -9963,22 +9963,22 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>回塘增重、品质/尺寸准入、金≈卖价×0.7+熟练度；收杆+背包入口</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/回鱼机制.md</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>FEAT-GROUND-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>打窝机制</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10010,32 +10010,32 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>Overlay并列循环打窝；50层非线性；0.5~1.5%/层曲线；附近鱼小幅尺寸</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/打窝机制.md</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>FEAT-ALBUM-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>钓鱼相册与成就</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10067,32 +10067,32 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>个人中心大改：资料+展示柜+图鉴+相册墙+成就；他人可见精选</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/钓鱼相册与成就.md</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>FEAT-RETURN-02</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>双价塘与自动回鱼</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>进塘二选一收费；可回鱼档达标自动回鱼；不可回鱼档仅出售</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/双价塘与自动回鱼.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10161,17 +10161,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>BUG-23</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>日额度满后仍可开钓</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10191,22 +10191,22 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>扣满4次/满8h不可start；可落座；对齐Web</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/BUG修复-日额度满后仍可开钓.md</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10300,27 +10300,27 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10362,22 +10362,22 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10419,22 +10419,22 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10471,27 +10471,27 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10528,27 +10528,27 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10590,22 +10590,22 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10731,17 +10731,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10756,17 +10756,17 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -10788,17 +10788,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10813,39 +10813,39 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FEAT-RETURN-01</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>回鱼机制</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10865,40 +10865,44 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>回塘增重、品质/尺寸准入、金≈卖价×0.7+熟练度；收杆+背包入口</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/回鱼机制.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FEAT-GROUND-01</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10908,7 +10912,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>打窝机制</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10918,40 +10922,44 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Overlay并列循环打窝；50层非线性；0.5~1.5%/层曲线；附近鱼小幅尺寸</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>docs/planning/specs/打窝机制.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FEAT-ALBUM-01</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10961,7 +10969,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>钓鱼相册与成就</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10971,30 +10979,148 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>个人中心大改：资料+展示柜+图鉴+相册墙+成就；他人可见精选</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓鱼相册与成就.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08I</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Bug 修复 / 功能优化</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>鱼塘退出与跨塘切换优化</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9460,7 +9460,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>暂缓；当前本机/局域网联机；上云仅改server.json切换；实施时再部署</t>
+          <t>方案已就绪(Windows手册)；实施可暂缓；上云仅改server.json；见docs/ops/windows-cloud-deploy.md</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:L197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>回塘增重、品质/尺寸准入、金≈卖价×0.7+熟练度；收杆+背包入口</t>
+          <t>回塘增重、紫品+体长比≥75%准入、金=卖价×1.5+熟练度；仅收费塘可回</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>进塘二选一收费；可回鱼档达标自动回鱼；不可回鱼档仅出售</t>
+          <t>进塘二选一收费；可回鱼档达标自动回鱼、不达标留包；免票塘不可回</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>FEAT-RETURN-03</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>回鱼规则调优</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10238,32 +10238,32 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>准入 purple/0.75 统一；回鱼金=卖价×1.5；仅收费塘可回；不达标留包</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/回鱼规则调优.md</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>FEAT-POOL-01</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>塘生态数值表驱动</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10305,22 +10305,22 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>种池表驱动；按塘类型品质权重；品质尺寸/咬钩脱钩基数入表；公式不变</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/塘生态数值表驱动.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>FEAT-FISH-CN-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>中国鱼种与区域分布</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10362,22 +10362,22 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>50种本土鱼库；塘真实钓场名；pond_fish_pool出鱼；pondId不变</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/中国鱼种与区域分布.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>FEAT-SPOT-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>钓位标签与线索库v2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10409,54 +10409,54 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>22类标签×420点位；154条合规线索；activitySignal；标签过滤线索；体长XP^0.85</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/钓位标签与线索库-v2.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>FEAT-SPOT-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>钓位标签地形微调</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10466,54 +10466,49 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>xlsx pond_spot_tags 420点按Tile岸位与真实地形人工微调标签</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/钓位标签地形微调.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>FEAT-SPOT-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>线索文案策划审校</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10523,44 +10518,39 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>spot_clue_texts 增删文案；遵守 habitat/activity 禁区；每 tag≥10 条</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/线索文案策划审校.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>FEAT-SPOT-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10570,7 +10560,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>钓位鱼情联动线索</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10580,7 +10570,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10590,22 +10580,17 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>生态 v2：钓位鱼量/迁移/受惊→computedTier；activity 线索匹配 activitySignal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/钓位鱼情联动线索.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10602,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10627,7 +10612,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10647,22 +10632,22 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10659,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10684,7 +10669,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10704,22 +10689,22 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10716,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10741,7 +10726,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10756,27 +10741,27 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10773,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10798,7 +10783,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10813,27 +10798,27 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10830,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10855,7 +10840,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10870,27 +10855,27 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10887,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10912,7 +10897,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10932,17 +10917,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -10959,7 +10944,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10969,7 +10954,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10984,22 +10969,22 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11016,17 +11001,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11046,12 +11031,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11073,50 +11058,449 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08B</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>商店与装备</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08C</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>动态墙与好友动态</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08D</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>排行榜</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I197" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
+      <c r="J197" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="K197" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11503,6 +11503,63 @@
       <c r="K197" t="inlineStr">
         <is>
           <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FEAT-RETURN-04</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>自动回鱼体验闭环</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>v0.7</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>回鱼档钓到即回；结算页；fish_catch_settled；Debug顶层弹窗；Debug发鱼不自动回</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/自动回鱼体验闭环.md</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Unity 960×480 Canvas Prefab 导出布局 JSON；Overlay 按像素表摆图与钓位，有表则停用 MapToScene</t>
+          <t>Unity 960×560 Canvas Prefab 导出布局 JSON；Overlay 按像素表摆图与钓位，有表则停用 MapToScene；不含 HUD</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>FEAT-RETURN-04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>自动回鱼体验闭环</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10622,32 +10622,32 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>回鱼档钓到即回；结算页；fish_catch_settled；Debug顶层弹窗；Debug发鱼不自动回</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/自动回鱼体验闭环.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-12B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Debug鱼塘钓位查看</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10679,32 +10679,32 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>Overlay Debug三列：塘/钓位鱼列表与属性、钓位数据、强制上钩；宽×1.3</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-Debug鱼塘钓位查看.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>FEAT-RETURN-05</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>回鱼体重分档</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10736,32 +10736,32 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>准入改体重&gt;10斤；&gt;100斤回鱼金×3、&gt;10斤×1.5；废弃紫品/体长比门槛</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/回鱼体重分档.md</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>FEAT-POOL-02</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>塘人口与品质权重调参</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10793,32 +10793,32 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>v0.7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>新手1条不补；公开塘上限100；补鱼60min；老手/野外水库/禁止品质占比定稿</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/塘人口与品质权重调参.md</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10860,12 +10860,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10969,27 +10969,27 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11031,22 +11031,22 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11088,22 +11088,22 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11140,27 +11140,27 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11202,22 +11202,22 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11254,17 +11254,17 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11368,17 +11368,17 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -11400,17 +11400,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11425,17 +11425,17 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -11457,17 +11457,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11482,22 +11482,22 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FEAT-RETURN-04</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>自动回鱼体验闭环</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11534,34 +11534,258 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>v0.7</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>回鱼档钓到即回；结算页；fish_catch_settled；Debug顶层弹窗；Debug发鱼不自动回</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/自动回鱼体验闭环.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08I</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Bug 修复 / 功能优化</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>鱼塘退出与跨塘切换优化</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-ART-03</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>美术</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>分塘底图、猫咪序列帧与 HUD 同步</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>每塘独立底图；六姿势序列帧目录与加载；Unity Overlay HUD Prefab 导出 JSON/PNG 后 Overlay 像素一一对应</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面Overlay分塘底图与HUD同步.md</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -9031,7 +9031,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9077,6 +9077,11 @@
       <c r="J154" t="inlineStr">
         <is>
           <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10830,17 +10835,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-ART-03</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>美术</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>分塘底图、猫咪序列帧与 HUD 同步</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10860,22 +10865,22 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>每塘独立底图；六姿势序列帧目录与加载；Unity Overlay HUD Prefab 导出 JSON/PNG 后 Overlay 像素一一对应</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面Overlay分塘底图与HUD同步.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10892,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10897,7 +10902,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10917,7 +10922,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10944,7 +10949,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10954,7 +10959,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10974,7 +10979,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10989,7 +10994,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11006,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11011,7 +11016,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11031,7 +11036,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11046,7 +11051,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11063,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11068,7 +11073,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11088,12 +11093,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11103,7 +11108,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11120,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11125,7 +11130,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11145,12 +11150,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11172,7 +11177,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11182,7 +11187,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11197,22 +11202,22 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11229,7 +11234,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11239,7 +11244,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11254,22 +11259,22 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11286,7 +11291,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11296,7 +11301,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11316,12 +11321,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11331,7 +11336,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11348,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11353,7 +11358,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11368,17 +11373,17 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11388,7 +11393,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11405,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11410,7 +11415,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11430,12 +11435,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11445,7 +11450,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11462,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11467,7 +11472,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11487,12 +11492,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11502,7 +11507,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11519,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11524,7 +11529,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11539,17 +11544,17 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11559,7 +11564,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11576,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11581,7 +11586,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11601,12 +11606,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11628,17 +11633,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11658,12 +11663,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11685,17 +11690,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11715,44 +11720,44 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-ART-03</t>
+          <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>美术</t>
+          <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>分塘底图、猫咪序列帧与 HUD 同步</t>
+          <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11772,20 +11777,24 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>每塘独立底图；六姿势序列帧目录与加载；Unity Overlay HUD Prefab 导出 JSON/PNG 后 Overlay 像素一一对应</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面Overlay分塘底图与HUD同步.md</t>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10892,7 +10892,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-13</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Overlay HUD 聊天栏与预制体对齐</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -10922,22 +10922,22 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>聊天栏默认一行向上展开；dock_chat 相对坐标；导出修复嵌套控件尺寸</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-13OverlayHUD聊天栏与预制体对齐.md</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-13A</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay 场景四边半透明渐隐</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10979,22 +10979,22 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>仅场景层 Absolute 渐隐；四边 40px；HUD 不参与；修复底部 mask 跟包围盒走</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-13AOverlay场景边缘半透明渐隐.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11006,17 +11006,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-13B</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>Overlay 宠物标签、右键与登录窗</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11036,22 +11036,22 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>状态/名字徽章；waiting→钓鱼中；右键他人社交菜单；DesktopShell scale=0 修复</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-13BOverlay宠物标签右键与登录窗.md</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-13C</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>Overlay 打窝 HUD 收口</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11093,22 +11093,22 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>按钮仅「打窝n/50」；成功文案走 txt_error；txt_error 移到钓鱼条上方</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-13COverlay打窝HUD收口.md</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11120,17 +11120,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-14</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>Overlay 透明区点击穿透回归</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11150,34 +11150,34 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>透明像素点穿桌面；保留13A四边40px渐隐；勿用#01000000整层抢命中</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面端-14Overlay透明点击穿透回归.md</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-14A</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>Overlay 座位预制体与空位显隐</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11207,34 +11207,29 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>OverlayPondActor为座位真相；塘内摆实例；猫跟actor-pet；空位半透明/落座隐藏</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-14AOverlay钓位座位图.md</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-14B</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11244,7 +11239,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>Overlay 横轴场景平移</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11254,7 +11249,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11264,44 +11259,39 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>场景宽默认1920视口960；左右箭头长按平滑平移；HUD与渐隐不跟移</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端-14BOverlay横轴场景平移.md</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-14C</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>美术</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>Overlay HUD 正式素材与文字对齐</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11311,7 +11301,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11321,34 +11311,29 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>Prefab换正式图；导出字体/字号/对齐；停止强制左对齐；动态文案不烤进PNG</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端-14COverlayHUD正式素材与文字对齐.md</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-14D</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11358,7 +11343,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>Overlay 宠物状态图标与上钩圆环</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11368,7 +11353,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11378,22 +11363,17 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>取消头顶相位字；小图标；圆环套在64猫身外圈；时长仍仅悬停</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-14DOverlay宠物状态图标与上钩圆环.md</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11385,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11415,7 +11395,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11430,27 +11410,27 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11442,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11472,7 +11452,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11487,27 +11467,27 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11499,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11529,7 +11509,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11544,27 +11524,27 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11556,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11586,7 +11566,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11606,22 +11586,22 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11613,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11643,7 +11623,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11663,17 +11643,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -11690,17 +11670,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11720,17 +11700,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -11747,50 +11727,563 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-07G</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>原生桌面宠物 Overlay</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08A</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>世界地图与鱼塘选择</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08B</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>商店与装备</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08C</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>动态墙与好友动态</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08D</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>排行榜</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I211" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
+      <c r="J211" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -11172,7 +11172,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11218,13 +11218,18 @@
       <c r="J192" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11270,13 +11275,18 @@
       <c r="J193" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11322,13 +11332,18 @@
       <c r="J194" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11374,6 +11389,11 @@
       <c r="J195" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-15</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Overlay 钓鱼栏按钮时序</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11435,22 +11435,22 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>主按钮常驻改文案；打窝后开钓须藏打窝；收杆结束后同时出打窝+离席；打窝中离席可打断</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-15Overlay钓鱼栏按钮时序.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-16</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay 窗口视口缩放</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11492,22 +11492,22 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>右键切960/800/600视口；高度切顶；HUD随宽内收；禁止整窗比例缩放</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-16Overlay窗口视口缩放.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11772,22 +11772,22 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11834,17 +11834,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11886,27 +11886,27 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11943,17 +11943,17 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12000,17 +12000,17 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12114,17 +12114,17 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12171,17 +12171,17 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12203,17 +12203,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12260,50 +12260,164 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I213" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
+      <c r="J213" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12422,6 +12422,165 @@
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-17</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>占用座位不可顶机器人</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>点bot/真人占用座不take_spot、不踢该座bot；塘满腾位保留</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-17占用座位不可顶机器人.md</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BUG-24</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Overlay形象进游戏不恢复</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>冷启动用已保存avatar；不必再打开个人中心保存</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Overlay形象进游戏不恢复.md</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BUG-25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Overlay打窝按钮剩余口数</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>按钮只打窝n/50；去掉bitesLeft后缀（-12实为剩余口数）</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Overlay打窝按钮剩余口数.md</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/项目开发需求计划表.xlsx
+++ b/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-17</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>占用座位不可顶机器人</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11549,22 +11549,22 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>点bot/真人占用座不take_spot、不踢该座bot；塘满腾位保留</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-17占用座位不可顶机器人.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11576,17 +11576,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>BUG-24</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay形象进游戏不恢复</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -11606,22 +11606,22 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>冷启动用已保存avatar；不必再打开个人中心保存</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Overlay形象进游戏不恢复.md</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11633,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>BUG-25</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>Overlay打窝按钮剩余口数</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11663,22 +11663,22 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>按钮只打窝n/50；去掉bitesLeft后缀（-12实为剩余口数）</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Overlay打窝按钮剩余口数.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11690,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>BUG-26</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>Overlay悬停与右键菜单指针命中</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -11720,22 +11720,22 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>猫身命中同一条链；菜单StaysOpen+右键抬起打开；悬停用自有开关不信IsOpen；关菜单后GetCursorPos恢复</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Overlay悬停与右键菜单指针命中.md</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-18</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>Overlay悬停浮窗条数与hint定位</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -11777,22 +11777,22 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>浮窗两行时长+钓到N条/空军；锚在actor-hint；命中问题归BUG-26</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面端-18Overlay悬停浮窗条数与hint定位.md</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-14E</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>Overlay头顶状态图标与进度环</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11834,22 +11834,22 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>等鱼无图标；仅上钩/打窝出icon；环改actor-ring+ring-bg，不再套猫</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-14EOverlay头顶状态图标与进度环.md</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11886,27 +11886,27 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11948,22 +11948,22 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12005,22 +12005,22 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12057,27 +12057,27 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12114,27 +12114,27 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12171,27 +12171,27 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12228,22 +12228,22 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12317,17 +12317,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12374,17 +12374,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12399,39 +12399,39 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-17</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>占用座位不可顶机器人</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12451,50 +12451,54 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>点bot/真人占用座不take_spot、不踢该座bot；塘满腾位保留</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-17占用座位不可顶机器人.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BUG-24</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Overlay形象进游戏不恢复</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12504,50 +12508,54 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>冷启动用已保存avatar；不必再打开个人中心保存</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay形象进游戏不恢复.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BUG-25</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Overlay打窝按钮剩余口数</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12557,7 +12565,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12567,20 +12575,195 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>按钮只打窝n/50；去掉bitesLeft后缀（-12实为剩余口数）</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay打窝按钮剩余口数.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08I</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Bug 修复 / 功能优化</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>鱼塘退出与跨塘切换优化</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>
